--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table114.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table114.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
@@ -145,8 +145,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -224,28 +224,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="2"/>
@@ -376,7 +376,7 @@
     <cacheField name="Oth Hrs" numFmtId="2">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
     </cacheField>
-    <cacheField name="Comp Rate Used" numFmtId="168">
+    <cacheField name="Comp Rate Used" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
     </cacheField>
     <cacheField name="Oth Earns" numFmtId="2">
@@ -4507,7 +4507,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="168" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField dataField="1" numFmtId="2" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
@@ -4651,10 +4651,10 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="1">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -4938,25 +4938,25 @@
       <c r="B1"/>
     </row>
     <row r="2" spans="1:5" ht="23.5">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="21">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" ht="15.5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5201,10 +5201,10 @@
       </c>
     </row>
     <row r="38" spans="1:2" s="1" customFormat="1" ht="15.5">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>129686</v>
       </c>
     </row>
